--- a/GFL_Fixed_Asset_RCM.xlsx
+++ b/GFL_Fixed_Asset_RCM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\AmazonDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA0719F-A0BC-4C40-A6BC-F538424C961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C061E8F-2ACA-4954-AB78-2E3894051065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1255,6 +1255,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="IM (Rectified by DTT) (2)"/>
       <sheetName val="IM (Rectified by DTT)"/>
